--- a/rcads/data/xls/30_Codebooks.xlsx
+++ b/rcads/data/xls/30_Codebooks.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_30_Codebooks"/>
   </sheets>
   <definedNames>
-    <definedName name="_30_Codebooks">'_30_Codebooks'!$A$1:$D$39</definedName>
+    <definedName name="_30_Codebooks">'_30_Codebooks'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -976,6 +976,38 @@
         <v>39</v>
       </c>
     </row>
+    <row outlineLevel="0" r="40">
+      <c r="A40" s="0">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>4.0-item-Frequency-Italian</t>
+        </is>
+      </c>
+      <c r="C40" s="0">
+        <v>1</v>
+      </c>
+      <c r="D40" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="41">
+      <c r="A41" s="0">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>4.0-item-Frequency-Zulu</t>
+        </is>
+      </c>
+      <c r="C41" s="0">
+        <v>1</v>
+      </c>
+      <c r="D41" s="0">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/rcads/data/xls/30_Codebooks.xlsx
+++ b/rcads/data/xls/30_Codebooks.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_30_Codebooks"/>
   </sheets>
   <definedNames>
-    <definedName name="_30_Codebooks">'_30_Codebooks'!$A$1:$D$41</definedName>
+    <definedName name="_30_Codebooks">'_30_Codebooks'!$A$1:$D$44</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1008,6 +1008,54 @@
         <v>41</v>
       </c>
     </row>
+    <row outlineLevel="0" r="42">
+      <c r="A42" s="0">
+        <v>41</v>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>4.0-item-Frequency-Chichewa</t>
+        </is>
+      </c>
+      <c r="C42" s="0">
+        <v>1</v>
+      </c>
+      <c r="D42" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="43">
+      <c r="A43" s="0">
+        <v>42</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>4.1-item-Frequency-Chichewa</t>
+        </is>
+      </c>
+      <c r="C43" s="0">
+        <v>1</v>
+      </c>
+      <c r="D43" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="44">
+      <c r="A44" s="0">
+        <v>43</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>4.0-item-Frequency-Bengali</t>
+        </is>
+      </c>
+      <c r="C44" s="0">
+        <v>1</v>
+      </c>
+      <c r="D44" s="0">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
